--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>57195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
